--- a/_data/cb-demoo.xlsx
+++ b/_data/cb-demoo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iancollins/Desktop/onemore/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E66CD767-46F3-6142-B1B9-2CFBF4B47147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{843A684C-C3B5-C945-BCD2-FEACC1F6514D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8740" yWindow="600" windowWidth="28040" windowHeight="16840" xr2:uid="{2FB0EF59-3DDD-4042-9F5A-5BD39C2815F1}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="547">
   <si>
     <t>objectid</t>
   </si>
@@ -1658,6 +1658,9 @@
   </si>
   <si>
     <t>World Cup Memo</t>
+  </si>
+  <si>
+    <t>multiple-page; memo</t>
   </si>
 </sst>
 </file>
@@ -6820,6 +6823,9 @@
       <c r="V69" t="s">
         <v>495</v>
       </c>
+      <c r="X69" t="s">
+        <v>76</v>
+      </c>
       <c r="Y69" t="s">
         <v>37</v>
       </c>
@@ -6846,6 +6852,9 @@
       <c r="V70" t="s">
         <v>495</v>
       </c>
+      <c r="X70" t="s">
+        <v>76</v>
+      </c>
       <c r="Y70" t="s">
         <v>37</v>
       </c>
@@ -6878,6 +6887,9 @@
       <c r="V71" t="s">
         <v>495</v>
       </c>
+      <c r="X71" t="s">
+        <v>76</v>
+      </c>
       <c r="Y71" t="s">
         <v>37</v>
       </c>
@@ -6904,6 +6916,9 @@
       <c r="V72" t="s">
         <v>495</v>
       </c>
+      <c r="X72" t="s">
+        <v>76</v>
+      </c>
       <c r="Y72" t="s">
         <v>37</v>
       </c>
@@ -6933,6 +6948,9 @@
       <c r="V73" t="s">
         <v>495</v>
       </c>
+      <c r="X73" t="s">
+        <v>76</v>
+      </c>
       <c r="Y73" t="s">
         <v>37</v>
       </c>
@@ -6965,6 +6983,9 @@
       <c r="V74" t="s">
         <v>495</v>
       </c>
+      <c r="X74" t="s">
+        <v>76</v>
+      </c>
       <c r="Y74" t="s">
         <v>37</v>
       </c>
@@ -6997,6 +7018,9 @@
       <c r="V75" t="s">
         <v>495</v>
       </c>
+      <c r="X75" t="s">
+        <v>76</v>
+      </c>
       <c r="Y75" t="s">
         <v>37</v>
       </c>
@@ -7029,6 +7053,9 @@
       <c r="V76" t="s">
         <v>495</v>
       </c>
+      <c r="X76" t="s">
+        <v>76</v>
+      </c>
       <c r="Y76" t="s">
         <v>37</v>
       </c>
@@ -7061,6 +7088,9 @@
       <c r="V77" t="s">
         <v>495</v>
       </c>
+      <c r="X77" t="s">
+        <v>76</v>
+      </c>
       <c r="Y77" t="s">
         <v>37</v>
       </c>
@@ -7090,6 +7120,9 @@
       <c r="V78" t="s">
         <v>495</v>
       </c>
+      <c r="X78" t="s">
+        <v>76</v>
+      </c>
       <c r="Y78" t="s">
         <v>37</v>
       </c>
@@ -7119,6 +7152,9 @@
       <c r="V79" t="s">
         <v>495</v>
       </c>
+      <c r="X79" t="s">
+        <v>76</v>
+      </c>
       <c r="Y79" t="s">
         <v>37</v>
       </c>
@@ -7148,6 +7184,9 @@
       <c r="V80" t="s">
         <v>495</v>
       </c>
+      <c r="X80" t="s">
+        <v>76</v>
+      </c>
       <c r="Y80" t="s">
         <v>37</v>
       </c>
@@ -7177,6 +7216,9 @@
       <c r="V81" t="s">
         <v>495</v>
       </c>
+      <c r="X81" t="s">
+        <v>76</v>
+      </c>
       <c r="Y81" t="s">
         <v>37</v>
       </c>
@@ -7206,6 +7248,9 @@
       <c r="V82" t="s">
         <v>495</v>
       </c>
+      <c r="X82" t="s">
+        <v>76</v>
+      </c>
       <c r="Y82" t="s">
         <v>37</v>
       </c>
@@ -7222,6 +7267,24 @@
       </c>
       <c r="E83" t="s">
         <v>80</v>
+      </c>
+      <c r="I83">
+        <v>1994</v>
+      </c>
+      <c r="K83" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>494</v>
+      </c>
+      <c r="V83" t="s">
+        <v>495</v>
+      </c>
+      <c r="X83" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
